--- a/docs/VitalsUnits.xlsx
+++ b/docs/VitalsUnits.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Terminology Maps VitalsUnits </t>
+    <t>Terminology Maps VitalsUnits</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/VitalsUnits.xlsx
+++ b/docs/VitalsUnits.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/VitalsUnits.xlsx
+++ b/docs/VitalsUnits.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="63">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -523,7 +523,9 @@
       <c r="D3" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" t="s" s="2">
+        <v>37</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -538,7 +540,9 @@
       <c r="D4" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="E4" s="2"/>
+      <c r="E4" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -553,7 +557,9 @@
       <c r="D5" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="E5" s="2"/>
+      <c r="E5" t="s" s="2">
+        <v>43</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">

--- a/docs/VitalsUnits.xlsx
+++ b/docs/VitalsUnits.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/VitalsUnits.xlsx
+++ b/docs/VitalsUnits.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/VitalsUnits.xlsx
+++ b/docs/VitalsUnits.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/VitalsUnits.xlsx
+++ b/docs/VitalsUnits.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/VitalsUnits.xlsx
+++ b/docs/VitalsUnits.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/VitalsUnits.xlsx
+++ b/docs/VitalsUnits.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
